--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.02021435885582</v>
+        <v>4.715784833314071</v>
       </c>
       <c r="D2" t="n">
-        <v>29.19684925753632</v>
+        <v>4.744488004349653</v>
       </c>
       <c r="E2" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F2" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.32980343768377</v>
+        <v>2.166093058623613</v>
       </c>
       <c r="D3" t="n">
-        <v>13.04434642902797</v>
+        <v>2.119706294717046</v>
       </c>
       <c r="E3" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F3" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.61643338213219</v>
+        <v>5.462670424596482</v>
       </c>
       <c r="D4" t="n">
-        <v>25.36583974390748</v>
+        <v>4.121948958384966</v>
       </c>
       <c r="E4" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F4" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.98490302202813</v>
+        <v>2.272546741079571</v>
       </c>
       <c r="D5" t="n">
-        <v>7.204370297873984</v>
+        <v>1.170710173404522</v>
       </c>
       <c r="E5" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F5" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.07862594740497</v>
+        <v>7.975276716453308</v>
       </c>
       <c r="D6" t="n">
-        <v>17.76580044774122</v>
+        <v>2.886942572757949</v>
       </c>
       <c r="E6" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F6" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.87461811334195</v>
+        <v>9.892125443418067</v>
       </c>
       <c r="D7" t="n">
-        <v>39.19270243241142</v>
+        <v>6.368814145266855</v>
       </c>
       <c r="E7" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F7" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.79394280287826</v>
+        <v>10.36651570546772</v>
       </c>
       <c r="D8" t="n">
-        <v>44.21738194897392</v>
+        <v>7.185324566708261</v>
       </c>
       <c r="E8" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F8" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.17368406391109</v>
+        <v>8.640723660385552</v>
       </c>
       <c r="D9" t="n">
-        <v>24.40946260136071</v>
+        <v>3.966537672721115</v>
       </c>
       <c r="E9" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F9" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.03373955015654</v>
+        <v>6.017982676900438</v>
       </c>
       <c r="D10" t="n">
-        <v>15.37254630492724</v>
+        <v>2.498038774550676</v>
       </c>
       <c r="E10" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F10" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.10260002566051</v>
+        <v>6.679172504169832</v>
       </c>
       <c r="D11" t="n">
-        <v>41.03006456769305</v>
+        <v>6.667385492250121</v>
       </c>
       <c r="E11" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F11" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.17215989388227</v>
+        <v>7.34047598275587</v>
       </c>
       <c r="D12" t="n">
-        <v>35.51651434723613</v>
+        <v>5.771433581425872</v>
       </c>
       <c r="E12" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F12" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.00487643738933</v>
+        <v>6.500792421075766</v>
       </c>
       <c r="D13" t="n">
-        <v>39.82928716112906</v>
+        <v>6.472259163683472</v>
       </c>
       <c r="E13" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F13" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.12224441617949</v>
+        <v>2.457364717629168</v>
       </c>
       <c r="D14" t="n">
-        <v>35.76436910310081</v>
+        <v>5.811709979253882</v>
       </c>
       <c r="E14" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F14" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.85821270937525</v>
+        <v>7.451959565273478</v>
       </c>
       <c r="D15" t="n">
-        <v>45.64520257972077</v>
+        <v>7.417345419204625</v>
       </c>
       <c r="E15" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F15" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>35.51372257834377</v>
+        <v>5.770979918980863</v>
       </c>
       <c r="D16" t="n">
-        <v>35.30603352772848</v>
+        <v>5.737230448255878</v>
       </c>
       <c r="E16" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F16" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.81003330617261</v>
+        <v>5.981630412253049</v>
       </c>
       <c r="D17" t="n">
-        <v>36.84674616058676</v>
+        <v>5.987596251095349</v>
       </c>
       <c r="E17" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F17" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>24.8459200517064</v>
+        <v>4.03746200840229</v>
       </c>
       <c r="D18" t="n">
-        <v>24.73985134034467</v>
+        <v>4.020225842806009</v>
       </c>
       <c r="E18" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F18" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.89607975774929</v>
+        <v>4.208112960634261</v>
       </c>
       <c r="D19" t="n">
-        <v>25.69470810590778</v>
+        <v>4.175390067210015</v>
       </c>
       <c r="E19" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F19" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>24.81029813422483</v>
+        <v>4.031673446811536</v>
       </c>
       <c r="D20" t="n">
-        <v>40.65699679646603</v>
+        <v>6.60676197942573</v>
       </c>
       <c r="E20" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F20" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>13.69964556624247</v>
+        <v>2.226192404514401</v>
       </c>
       <c r="D21" t="n">
-        <v>20.12159135020807</v>
+        <v>3.269758594408811</v>
       </c>
       <c r="E21" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F21" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>18.90988367607774</v>
+        <v>3.072856097362633</v>
       </c>
       <c r="D22" t="n">
-        <v>9.809990465381588</v>
+        <v>1.594123450624508</v>
       </c>
       <c r="E22" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F22" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>38.69029876583585</v>
+        <v>6.287173549448325</v>
       </c>
       <c r="D23" t="n">
-        <v>38.51381943158831</v>
+        <v>6.258495657633101</v>
       </c>
       <c r="E23" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F23" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>34.0452590271878</v>
+        <v>5.532354591918017</v>
       </c>
       <c r="D24" t="n">
-        <v>17.63138829214831</v>
+        <v>2.8651005974741</v>
       </c>
       <c r="E24" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F24" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>14.63767502833851</v>
+        <v>2.378622192105008</v>
       </c>
       <c r="D25" t="n">
-        <v>14.56696036446221</v>
+        <v>2.367131059225109</v>
       </c>
       <c r="E25" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F25" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>44.01076538744682</v>
+        <v>7.151749375460108</v>
       </c>
       <c r="D26" t="n">
-        <v>1.602562343919406</v>
+        <v>0.2604163808869034</v>
       </c>
       <c r="E26" t="n">
-        <v>14.36093478836731</v>
+        <v>2.333651903109689</v>
       </c>
       <c r="F26" t="n">
-        <v>12.40355264853068</v>
+        <v>2.015577305386236</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
